--- a/خصومات بصريات.xlsx
+++ b/خصومات بصريات.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Omar\waad_temp_website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{560B6FE3-B958-4340-A5B3-8FB9C5CB545F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDFE5DF5-C29F-41D9-B2BE-C36F6841354C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3444" uniqueCount="2018">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3446" uniqueCount="2020">
   <si>
     <t>اسم المريض</t>
   </si>
@@ -6123,12 +6121,18 @@
   <si>
     <t>HJR000</t>
   </si>
+  <si>
+    <t>WAB2025004855</t>
+  </si>
+  <si>
+    <t>WAB2025004915</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6186,16 +6190,19 @@
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="14"/>
@@ -6227,7 +6234,7 @@
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="14"/>
@@ -6255,7 +6262,7 @@
       <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -6284,26 +6291,33 @@
       <sz val="14"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="14"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFFF0000"/>
+      <name val="Tajawal"/>
     </font>
   </fonts>
   <fills count="7">
@@ -6638,7 +6652,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="204">
+  <cellXfs count="206">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment readingOrder="2"/>
@@ -7230,6 +7244,10 @@
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -18639,42 +18657,42 @@
       </c>
     </row>
     <row r="589" spans="1:6" ht="18" x14ac:dyDescent="0.35">
-      <c r="A589" s="15" t="s">
+      <c r="A589" s="98" t="s">
         <v>1491</v>
       </c>
-      <c r="B589" s="102">
-        <v>4855</v>
-      </c>
-      <c r="C589" s="117" t="s">
+      <c r="B589" s="204" t="s">
+        <v>2018</v>
+      </c>
+      <c r="C589" s="205" t="s">
         <v>97</v>
       </c>
-      <c r="D589" s="15" t="s">
+      <c r="D589" s="98" t="s">
         <v>423</v>
       </c>
-      <c r="E589" s="15">
+      <c r="E589" s="98">
         <v>280</v>
       </c>
-      <c r="F589" s="15" t="s">
+      <c r="F589" s="98" t="s">
         <v>1492</v>
       </c>
     </row>
     <row r="590" spans="1:6" ht="18" x14ac:dyDescent="0.35">
-      <c r="A590" s="15" t="s">
+      <c r="A590" s="98" t="s">
         <v>1493</v>
       </c>
-      <c r="B590" s="102">
-        <v>4915</v>
-      </c>
-      <c r="C590" s="117" t="s">
+      <c r="B590" s="204" t="s">
+        <v>2019</v>
+      </c>
+      <c r="C590" s="205" t="s">
         <v>98</v>
       </c>
-      <c r="D590" s="15" t="s">
+      <c r="D590" s="98" t="s">
         <v>423</v>
       </c>
-      <c r="E590" s="15">
+      <c r="E590" s="98">
         <v>300</v>
       </c>
-      <c r="F590" s="15" t="s">
+      <c r="F590" s="98" t="s">
         <v>1494</v>
       </c>
     </row>
